--- a/src/attributions/attributions_ig_traj_380.xlsx
+++ b/src/attributions/attributions_ig_traj_380.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1369142162634061</v>
+        <v>0.1502397507993557</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01614333871291241</v>
+        <v>-0.03176905575942954</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0379392985842668</v>
+        <v>-0.03919651625920684</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1029,16 +1029,16 @@
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07308471405402833</v>
+        <v>0.1344317519449315</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00547327550959028</v>
+        <v>0.01252870795930967</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.03348182326508245</v>
+        <v>-0.0380287831716425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1050,31 +1050,31 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07393332907853351</v>
+        <v>0.04933794293621747</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0429967819090275</v>
+        <v>0.006918890520727385</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03359579898757861</v>
+        <v>-0.01761780746128378</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1083,76 +1083,76 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.002881283057585238</v>
+        <v>0.07569507702000167</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.07610369797566786</v>
+        <v>-0.08308585038922449</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.03661456362739942</v>
+        <v>0.038428430708873</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02821201182324088</v>
+        <v>0.08637832904977008</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.06584714992567468</v>
+        <v>-0.02092666061815441</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06843110399543872</v>
+        <v>0.09082985469045393</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3426605073600978</v>
+        <v>0.3089797221005676</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.04563238967499481</v>
+        <v>-0.2021711828936082</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1309339948118897</v>
+        <v>-0.06765111673121502</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>-0</v>
@@ -1161,46 +1161,46 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1357696008369131</v>
+        <v>-0.037331806013213</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.0187018224100847</v>
+        <v>-0.01355099561603186</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.1717217191073227</v>
+        <v>-0.03345542265219548</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.006617909315195591</v>
+        <v>-0.05208521401167391</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.09252079638406122</v>
+        <v>0.02899781475738207</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.08037119782830192</v>
+        <v>0.095804182397955</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
@@ -1212,49 +1212,49 @@
         <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2271926023948005</v>
+        <v>0.1757768501798035</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04385271715983758</v>
+        <v>-0.1004926683001708</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.007965163057930021</v>
+        <v>-0.01952398373491702</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.07060315067651107</v>
+        <v>-0.1388229574135958</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0277329392206911</v>
+        <v>0.0855638497887786</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.03476471284845755</v>
+        <v>0.02179135557463267</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
@@ -1266,25 +1266,25 @@
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01182493055148366</v>
+        <v>-0.02090222356823698</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.02328782858797997</v>
+        <v>0.01784436575777125</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.04505660832767891</v>
+        <v>-0.006809155654508104</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,22 +1293,22 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.07505303658875609</v>
+        <v>-0.1520499145689488</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04779900288514672</v>
+        <v>0.09191312690493045</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.03381328063741882</v>
+        <v>0.03711604781176394</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
@@ -1320,139 +1320,139 @@
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.02354223304621417</v>
+        <v>-0.1073634561086754</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.06266816687738799</v>
+        <v>0.05875952705061702</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.02149451821506314</v>
+        <v>-0.02809562082619812</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02942717681079304</v>
+        <v>-0.08832159437230352</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.05610502995343604</v>
+        <v>0.07683116935089361</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.03008690416419722</v>
+        <v>-0.08516167102877377</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.03040252677446015</v>
+        <v>-0.08623305167234839</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.09062054611974553</v>
+        <v>0.02450772547502439</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02570181317855657</v>
+        <v>-0.005418514466160941</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1372638745048739</v>
+        <v>-0.0762150628467298</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.03135274961883417</v>
+        <v>0.06991976932592534</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03498653449756144</v>
+        <v>0.04507238334469012</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.005734289149696093</v>
+        <v>0.05633930564239158</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03231647713071129</v>
+        <v>0.02199878968521577</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03694082956636315</v>
+        <v>-0.02045869797714098</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,97 +1461,97 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.07220667964085083</v>
+        <v>-0.1630595554968984</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.03362393757812495</v>
+        <v>0.09809988400462642</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.04285670980274253</v>
+        <v>0.01274799164494493</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.0177623006338717</v>
+        <v>-0.0715536797178689</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.003231280934455525</v>
+        <v>-0.04739837781266828</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.02611478501686144</v>
+        <v>0.03124057604371947</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.05343568243417637</v>
+        <v>-0.1094268369854799</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.121263048702455</v>
+        <v>0.2649575398998003</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.0768325238863843</v>
+        <v>0.07832827148107442</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01946695448203289</v>
+        <v>-0.1077685958660648</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.00617118811163399</v>
+        <v>0.04584605866850628</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1568,100 +1568,100 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02258455527021038</v>
+        <v>-0.1314467576692383</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1783208537504497</v>
+        <v>0.3075663391910922</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02430370932501812</v>
+        <v>-0.122627868077738</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07054565459913602</v>
+        <v>-0.2367028229772166</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0003060617029985326</v>
+        <v>-0.08450246533495777</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06756611696189875</v>
+        <v>0.2980481946215973</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03895659069223012</v>
+        <v>-0.1542929752832722</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04569874173010362</v>
+        <v>-0.165284201659247</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004060363454562459</v>
+        <v>-0.02499548727296541</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02609411187526447</v>
+        <v>0.07985651877224477</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.08791830083587915</v>
+        <v>-0.2636558168149705</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0195835165003491</v>
+        <v>-0.3407652132556086</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04508776672774024</v>
+        <v>0.07719295767023289</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1682944604581341</v>
+        <v>0.1386290415933893</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1225079930067699</v>
+        <v>0.132270500820669</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1670,16 +1670,16 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1487955563671387</v>
+        <v>0.3155306023719204</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02478527890663718</v>
+        <v>-0.08841534239237457</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02364319176622437</v>
+        <v>0.2438600791989352</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.06025313503585144</v>
+        <v>0.1157835676370333</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1700,160 +1700,160 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.06527541088309922</v>
+        <v>-0.1464988634543995</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07226166021392402</v>
+        <v>-0.07848055648715699</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.248311376944774</v>
+        <v>0.6561104662085719</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.2852507423844232</v>
+        <v>-0.1176595979143652</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.1187816274123885</v>
+        <v>-0.3425752854108123</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.03730979558433681</v>
+        <v>0.02072929008660718</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.06958524745376245</v>
+        <v>-0.09019360869611859</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.1850633336670151</v>
+        <v>0.05147204641529417</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.07294285834668922</v>
+        <v>-0.3282174802437166</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.004715174159016633</v>
+        <v>0.0903382318286622</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.03029679228766944</v>
+        <v>0.07607218980248939</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1837628145470212</v>
+        <v>0.2759079206599581</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.05069004295982931</v>
+        <v>0.312026183138733</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.006620814879268575</v>
+        <v>-0.07176262231480002</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.185637838764524</v>
+        <v>0.4192048956243061</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.04960312806668302</v>
+        <v>-0.349808525959819</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.04693681909936791</v>
+        <v>-0.5978569116901862</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.01924044761641479</v>
+        <v>0.0796051184428016</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.09512900104394811</v>
+        <v>-0.283589797223283</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.02654668607740233</v>
+        <v>0.06318817406568222</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0782824286151864</v>
+        <v>0.2596099308742601</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.01159477915124158</v>
+        <v>-0.03083218382611457</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01008077974707818</v>
+        <v>-0.08902674568186279</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.02519737171126261</v>
+        <v>-0.06035729202528468</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
@@ -1862,49 +1862,49 @@
         <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0.008398952230449071</v>
+        <v>0.04207378527436648</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.01452921290483518</v>
+        <v>0.05565231244849408</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.110476545838435</v>
+        <v>-0.2858718798639651</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.04404239502912755</v>
+        <v>-0.01407082830108673</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0452543800883847</v>
+        <v>0.298338261522763</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07555647609700626</v>
+        <v>0.04338699649536747</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.3890934025976798</v>
+        <v>-0.5076722865315934</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2410377984282046</v>
+        <v>-0.1579689069245704</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
@@ -1913,16 +1913,16 @@
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.05485639950106998</v>
+        <v>0.0839499598232589</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001218729704758483</v>
+        <v>-0.06337832719135546</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.1318088749909414</v>
+        <v>-0.1651173503421324</v>
       </c>
       <c r="DP3" t="n">
         <v>-0</v>
@@ -1931,52 +1931,52 @@
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.02064759533772728</v>
+        <v>-0.01770865177511758</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.04217165916072044</v>
+        <v>-0.07018974991207469</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.03586070407410489</v>
+        <v>-0.02982351959588624</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.1419873310230666</v>
+        <v>-0.2007943522992388</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.002450683331216625</v>
+        <v>-0.2140624034963241</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1238063756939523</v>
+        <v>-0.1928425799685714</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.01219061075783407</v>
+        <v>0.1459592984706085</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.05122438005321606</v>
+        <v>-0.1670670710384412</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,88 +1985,88 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01358687924643079</v>
+        <v>0.03573745025741381</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.1129383666620049</v>
+        <v>0.2277703907112542</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.002865310075889172</v>
+        <v>0.03011706489482523</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1019226455486551</v>
+        <v>0.02466557686556627</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1366158740721332</v>
+        <v>-0.226111017650726</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.03298955097226319</v>
+        <v>0.1028052565666799</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.01475623996510193</v>
+        <v>0.07617452313055385</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.1222088021721207</v>
+        <v>-0.3527006096127691</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.07156557462646904</v>
+        <v>0.06594397926370016</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.01136530186581173</v>
+        <v>0.3139961124371499</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0.04393340141204721</v>
+        <v>0.09572848881815607</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.02029380987729145</v>
+        <v>-0.270826554512084</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.03553231215210649</v>
+        <v>-0.07568768653470739</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
@@ -2075,64 +2075,64 @@
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.03184740731541701</v>
+        <v>0.3394043035939115</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1062418538927641</v>
+        <v>0.1999061774067622</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.02376500198983611</v>
+        <v>-0.190912190208974</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1148456437643558</v>
+        <v>0.5944754342323471</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0.001704204397792203</v>
+        <v>0.04121382823956232</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.01217388140110762</v>
+        <v>0.1958544308935188</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.1437061890272653</v>
+        <v>-0.2230137628859637</v>
       </c>
       <c r="GA3" t="n">
         <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1261049127546481</v>
+        <v>0.4679217982182875</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1781994567097836</v>
+        <v>0.2924762259484858</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0275769994883336</v>
+        <v>-0.001186642116405263</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1846578549735124</v>
+        <v>-0.2496794069287613</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2167,22 +2167,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1145959160775341</v>
+        <v>0.2233033456444132</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.006721239833121691</v>
+        <v>-0.05270106559062887</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1201226312512365</v>
+        <v>-0.1567857168912547</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
@@ -2191,10 +2191,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008891355727385277</v>
+        <v>0.1043089710328944</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0348999213080316</v>
+        <v>-0.03759288053652893</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01809877692746069</v>
+        <v>-0.03950826450729687</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2215,25 +2215,25 @@
         <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01852743151079726</v>
+        <v>-0.03799948490671731</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0151214128137533</v>
+        <v>-0.08077936929652027</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.009362669174840464</v>
+        <v>-0.0271756473134495</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2242,28 +2242,28 @@
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05620275786064292</v>
+        <v>0.1434788658818093</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.06358457071167851</v>
+        <v>0.1244972396712149</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.130797199021089</v>
+        <v>-0.07108804028888228</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,25 +2272,25 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2680849414789708</v>
+        <v>0.6167630283586243</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.0514960811095423</v>
+        <v>0.005626727782373337</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.162485263667881</v>
+        <v>-0.2110879542476697</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>-0</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1371947854466842</v>
+        <v>0.03230477992273133</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02951986030672129</v>
+        <v>-0.01145882630282949</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.1398070586668425</v>
+        <v>-0.1822931163314191</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
@@ -2329,34 +2329,34 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.06234071473773829</v>
+        <v>-0.01367650060111582</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.07730053785574786</v>
+        <v>0.09770049238482438</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.006256632124854345</v>
+        <v>0.06310314254824402</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1248945836808727</v>
+        <v>0.320927723023949</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.03297648144044749</v>
+        <v>-0.03381316537957652</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.1109206127625226</v>
+        <v>-0.2484005729329532</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
@@ -2380,25 +2380,25 @@
         <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.08252812821851575</v>
+        <v>-0.2263405442735058</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.005838219457756915</v>
+        <v>-0.01046336297856622</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.06844555643676284</v>
+        <v>0.1476896809141144</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.01579520462501464</v>
+        <v>-0.0452638328386557</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,10 +2419,10 @@
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004428443275991372</v>
+        <v>-0.008966258992789191</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.0151677437931035</v>
+        <v>0.02310258556209888</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2434,25 +2434,25 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.06331614393429405</v>
+        <v>-0.2184485138956799</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01241175042664073</v>
+        <v>-0.002659401884692732</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.09330050803865932</v>
+        <v>0.1715115800163894</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
@@ -2461,55 +2461,55 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05995741776460795</v>
+        <v>-0.1717761568219562</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1144259774765505</v>
+        <v>-0.05092943927923217</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.02437918367437476</v>
+        <v>0.07036917071132105</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.04067122775312296</v>
+        <v>-0.09142617749071492</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.0511503051674831</v>
+        <v>-0.04016457998621274</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.03818403716785475</v>
+        <v>-0.0945892630497676</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,34 +2518,34 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.06044217191791914</v>
+        <v>-0.1264098214037948</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.02107854290239237</v>
+        <v>-0.1102506063007458</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.01765606402643339</v>
+        <v>0.1567885480386763</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.08334281995566929</v>
+        <v>-0.1167347932857347</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,67 +2554,67 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.06521009233995437</v>
+        <v>-0.06955263462012451</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.09781616683075123</v>
+        <v>0.08828816842535295</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.04105684596751995</v>
+        <v>0.04703837294506531</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.02827919167459628</v>
+        <v>0.07890387005929517</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.04224974716101221</v>
+        <v>0.09965810973203935</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.0569987719821684</v>
+        <v>-0.2405284876982002</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.009274002675837823</v>
+        <v>-0.04611528986742207</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.07548297601001264</v>
+        <v>0.1496017237779659</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
@@ -2626,25 +2626,25 @@
         <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01354741327111684</v>
+        <v>-0.2171860695436011</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.01703941074116405</v>
+        <v>0.157295217342232</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.09063367817001949</v>
+        <v>0.07467419300035541</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.1470210354791125</v>
+        <v>-0.3050282155392974</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,10 +2662,10 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.04542471268507599</v>
+        <v>-0.02957070636530407</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.07048817733666302</v>
+        <v>0.1014904486267097</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,25 +2674,25 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.04827281772359357</v>
+        <v>-0.1118817984886337</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.04019308501187425</v>
+        <v>0.1369647690133675</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1878859189787792</v>
+        <v>0.182501201719753</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.03297503106134766</v>
+        <v>-0.05735893432286091</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02581600216821339</v>
+        <v>-0.05042008397848523</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1030344855967241</v>
+        <v>0.1580741316140803</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05315489684484976</v>
+        <v>-0.09557212890711257</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02395364432876986</v>
+        <v>-0.054183121013436</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09488271695340474</v>
+        <v>0.09635265507220424</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005719481257055323</v>
+        <v>-0.02243685377189436</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06889951457122288</v>
+        <v>-0.03687878458460172</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -2790,43 +2790,43 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.02930270520436502</v>
+        <v>0.04959774562277942</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.007237447048326896</v>
+        <v>-0.1275326716428843</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.007280508994509606</v>
+        <v>0.0418996713098984</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01389858173755861</v>
+        <v>0.09228928517257019</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.044772495866134</v>
+        <v>-0.07916748290989048</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.04840336162898483</v>
+        <v>0.0983525098350015</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,31 +2835,31 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3382180598764375</v>
+        <v>0.418270983961148</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001124325459848943</v>
+        <v>-0.2040087348814169</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1383813322806143</v>
+        <v>-0.1119854376254522</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
@@ -2868,28 +2868,28 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03992341134461035</v>
+        <v>-0.08094610005690418</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03804209193782766</v>
+        <v>-0.006031620275353576</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1155671210799583</v>
+        <v>-0.05461144471547998</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,19 +2898,19 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06635997582068412</v>
+        <v>-0.03482161188695196</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05758180853879979</v>
+        <v>0.02857236239514704</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1156216787886627</v>
+        <v>0.09186544744160906</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2925,154 +2925,154 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1613345767633263</v>
+        <v>0.2102856174269616</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.00280202524134705</v>
+        <v>-0.1091570332884602</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.07817050341410924</v>
+        <v>-0.02892685256618555</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0770093249256936</v>
+        <v>-0.1368411781864766</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01989775243760825</v>
+        <v>0.1122001796654486</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02560780073057455</v>
+        <v>0.03501825677919605</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01152607951754111</v>
+        <v>-0.02687050158222309</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.01012645936911333</v>
+        <v>0.0305530039941488</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.02793509277469077</v>
+        <v>0.002174210153481806</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.06985457018752006</v>
+        <v>-0.1420124988724659</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03119012249268826</v>
+        <v>0.1120685504970656</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.01763759887736671</v>
+        <v>0.03039551173697272</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.03870540884138943</v>
+        <v>-0.080380452994987</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.06648856514616093</v>
+        <v>0.06711219806019564</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.02931159554192519</v>
+        <v>-0.07662962428915729</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.0258669639041006</v>
+        <v>-0.1101655226304786</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.07582098890712863</v>
+        <v>0.07093037800244427</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.003007305221380895</v>
+        <v>-0.05681854560960803</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3084,28 +3084,28 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.03659956898808564</v>
+        <v>-0.04636391033527754</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.05560375038561412</v>
+        <v>-0.07238220169672291</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02499520649381263</v>
+        <v>-0.008482862242275336</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,52 +3114,52 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.115659614594351</v>
+        <v>-0.09718361827824019</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.06077528239546574</v>
+        <v>0.08945937877334506</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04040579711183986</v>
+        <v>0.0723285260001436</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.04158713096451668</v>
+        <v>0.04881247501965932</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.01863503296053666</v>
+        <v>0.06933217093917601</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.05712652536998138</v>
+        <v>-0.0141398021733975</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
@@ -3168,106 +3168,106 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.07103428271406434</v>
+        <v>-0.1535738392444483</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03169562731388856</v>
+        <v>0.1250537455773463</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01688639545066735</v>
+        <v>0.01155019419733656</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.00383606268031789</v>
+        <v>-0.06267903753763832</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02203022467234553</v>
+        <v>0.001463522326884919</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.04773772868482297</v>
+        <v>0.008611830980339545</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.002457710880803252</v>
+        <v>-0.1235622879436304</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1112043644126783</v>
+        <v>0.2124151741934699</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.06758510817423426</v>
+        <v>0.1522978117086608</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.01854459877552412</v>
+        <v>-0.1369779905742915</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.03196888473868387</v>
+        <v>0.07175465078348964</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0946589092282354</v>
+        <v>-0.1153726930557741</v>
       </c>
       <c r="C6" t="n">
         <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0008858605321835206</v>
+        <v>-0.002466536044001174</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02617682645615032</v>
+        <v>0.03429968550682747</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3338936478630619</v>
+        <v>0.1362290940180916</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -3302,28 +3302,28 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05147575774498222</v>
+        <v>-0.1091168070210571</v>
       </c>
       <c r="L6" t="n">
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0007286315028597407</v>
+        <v>0.002355534409593369</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02419588320225177</v>
+        <v>0.0733483762776044</v>
       </c>
       <c r="O6" t="n">
-        <v>0.200026415009134</v>
+        <v>0.09215051801292154</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,49 +3332,49 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07869597295601211</v>
+        <v>-0.08120961170679343</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0803525096118726</v>
+        <v>0.04927552520863888</v>
       </c>
       <c r="W6" t="n">
-        <v>0.150075953489113</v>
+        <v>-0.05244095466151522</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1149434336480895</v>
+        <v>0.07549738994657963</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01583083609446007</v>
+        <v>0.01479039625428936</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.02317442238940717</v>
+        <v>0.05167818508198064</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.09259938888300064</v>
+        <v>0.03818075705056944</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.01730269630340307</v>
+        <v>-0.04848042268351645</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -3383,82 +3383,82 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.02833150984426263</v>
+        <v>-0.09205593954867469</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.03949987708506664</v>
+        <v>-0.0483845562259826</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.07772051403504281</v>
+        <v>-0.1336995647612698</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.1277200489706107</v>
+        <v>0.05614731064918671</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.07773411492214083</v>
+        <v>-0.3569919717969166</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.04412272265859477</v>
+        <v>-0.02637671754724369</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.122081883338507</v>
+        <v>-0.1066230677878276</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.4188419008815939</v>
+        <v>0.3026124199221401</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1968785576489146</v>
+        <v>0.1761115691498081</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1031652169952502</v>
+        <v>0.05939758702517103</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02385056246417696</v>
+        <v>0.1271873750345017</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.172526269856701</v>
+        <v>0.006977732443314034</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,79 +3467,79 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1737502861869405</v>
+        <v>-0.02174201290219355</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.106765954917068</v>
+        <v>-0.0659945135204917</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.04069396610334381</v>
+        <v>-0.1026068323699651</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.02978389835253668</v>
+        <v>0.01490668474097614</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.01593410289041616</v>
+        <v>-0.2151161188961808</v>
       </c>
       <c r="BW6" t="n">
         <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.08046469185261883</v>
+        <v>-0.03751641683752911</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1090120476022224</v>
+        <v>-0.06249567428305203</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.1609161780767214</v>
+        <v>0.2012228296439541</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.05536350395551505</v>
+        <v>0.1649371906040646</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01326413424715536</v>
+        <v>-0.01042479569909316</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.02721598234104353</v>
+        <v>-0.0164875662735183</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.1250850325462782</v>
+        <v>-0.08337639047679105</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
@@ -3548,22 +3548,22 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.001559550835090071</v>
+        <v>0.02932535938130328</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.02276833714370208</v>
+        <v>0.0268387670826695</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.02357421844368673</v>
+        <v>-0.002279407763742525</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01377513386251919</v>
+        <v>-0.03351111804395002</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
@@ -3572,28 +3572,28 @@
         <v>0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02542848007070721</v>
+        <v>0.1746594428035923</v>
       </c>
       <c r="CX6" t="n">
         <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.008801903446177201</v>
+        <v>-0.02133782435824242</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.02980108563020397</v>
+        <v>-0.04962710497366196</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.1378591728600652</v>
+        <v>-0.09126366237381518</v>
       </c>
       <c r="DB6" t="n">
         <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>-0</v>
@@ -3602,52 +3602,52 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0947407494732683</v>
+        <v>0.01243827600539231</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.1711303971782911</v>
+        <v>-0.03709848380048653</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.1551637835234786</v>
+        <v>0.07535159360752812</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.02112935332679984</v>
+        <v>-0.07131844849819147</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02752334755064678</v>
+        <v>0.1435802472839569</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.05507242152185324</v>
+        <v>0.03071546827405251</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.004335031447684345</v>
+        <v>0.008415369858407164</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05075138826692548</v>
+        <v>-0.0543926027280534</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,19 +3656,19 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.04046406445423494</v>
+        <v>0.10096889923798</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0009358999539177312</v>
+        <v>0.1393914785256985</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.02864945701159969</v>
+        <v>-0.003569171005211569</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.1209662731009032</v>
+        <v>0.1815632327601734</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
@@ -3677,25 +3677,25 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.009220108624999699</v>
+        <v>0.1292945365289122</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.08357729309144996</v>
+        <v>-0.05607174346169777</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.02628118753647925</v>
+        <v>-0.03703278270210733</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.1424902046658117</v>
+        <v>0.007628897448878055</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
@@ -3704,28 +3704,28 @@
         <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
         <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.01886328845746102</v>
+        <v>-0.003430992760958364</v>
       </c>
       <c r="EQ6" t="n">
         <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.08176321000758642</v>
+        <v>-0.02140846653489273</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0458238906068462</v>
+        <v>0.0160216701577084</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.01526699977402651</v>
+        <v>-0.007489445069354124</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
         <v>-0</v>
@@ -3734,52 +3734,52 @@
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.01941815688434378</v>
+        <v>0.1973117048160092</v>
       </c>
       <c r="EZ6" t="n">
         <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01603160997759093</v>
+        <v>-0.02540646333193172</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.06039273569762436</v>
+        <v>-0.02080889065022255</v>
       </c>
       <c r="FC6" t="n">
-        <v>-0.1305639766421692</v>
+        <v>-0.100138448693847</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.07152256432906538</v>
+        <v>0.1012561446760176</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.06014364219919099</v>
+        <v>0.1326243627418367</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.05461339553119321</v>
+        <v>0.01171960362994972</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0.1259435617432182</v>
+        <v>-0.0002667592632322998</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
@@ -3791,22 +3791,22 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.08056354643825843</v>
+        <v>0.277218021935461</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.004023491438747903</v>
+        <v>-0.2192216992641479</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1742825247824597</v>
+        <v>-0.03115193140399249</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0.03885156124052953</v>
+        <v>-0.07043275014429251</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
@@ -3815,28 +3815,28 @@
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01480839119108015</v>
+        <v>0.1267425977737188</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.08373795167658057</v>
+        <v>0.03106209481357276</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.09625269416058888</v>
+        <v>-0.02604980479520225</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -3847,34 +3847,34 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.09234778237382359</v>
+        <v>0.4477191288858487</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01315401999820447</v>
+        <v>-0.003490362244090275</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.05273608074131479</v>
+        <v>-0.2119773188261419</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06619439456740325</v>
+        <v>0.4373271172867064</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,70 +3883,70 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.006784754198319459</v>
+        <v>-0.111718884108232</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03309487681714047</v>
+        <v>-0.1377606238333732</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00764617571351165</v>
+        <v>0.08680909649850127</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02331273313473652</v>
+        <v>-0.09834841288171987</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.01259437340963619</v>
+        <v>-0.09655484502956706</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01653504897364372</v>
+        <v>0.1154208364507163</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01778832001045309</v>
+        <v>-0.1260889459440162</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02041779922809613</v>
+        <v>0.007365253530829801</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01325555347230723</v>
+        <v>0.1926266585731445</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.009186066528401881</v>
+        <v>0.0640795908333134</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04141379105696225</v>
+        <v>-0.1611452538259352</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,55 +3979,55 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1027389058919417</v>
+        <v>0.8274999417174017</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.009844116357784793</v>
+        <v>-0.3331400421443176</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.08188824518074574</v>
+        <v>-0.2678652602993087</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05218128303105522</v>
+        <v>0.04526098666846271</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.03716409997836195</v>
+        <v>-0.01366641588600607</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.02921921106308342</v>
+        <v>-0.2099453710936924</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>-0</v>
@@ -4036,34 +4036,34 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03860890255496944</v>
+        <v>0.1371865784287226</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01436216231845319</v>
+        <v>0.151431930638803</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.003052206848244927</v>
+        <v>0.0897463183746615</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.04741308838414109</v>
+        <v>0.5381893353601365</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0131330171962706</v>
+        <v>-0.1099059508442769</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.03797220254593873</v>
+        <v>-0.270279898381168</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>-0</v>
@@ -4087,49 +4087,49 @@
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02810761374821081</v>
+        <v>-0.2807260827635195</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001351774245725975</v>
+        <v>0.01562041591743929</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01955035241555076</v>
+        <v>0.1705661930586361</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0008595768701870824</v>
+        <v>-0.09293650318312985</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0006947239744261103</v>
+        <v>0.0340671813480778</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.004134798530054136</v>
+        <v>0.03800151136769912</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4141,22 +4141,22 @@
         <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02461277802634954</v>
+        <v>-0.2660680793124084</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.002347022316919947</v>
+        <v>-0.0121822200002325</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.02457646007615853</v>
+        <v>0.150004217862988</v>
       </c>
       <c r="DB7" t="n">
         <v>-0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.00878362971933809</v>
+        <v>-0.03621106023872436</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01762411016869538</v>
+        <v>-0.05994228806975614</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02626555177161751</v>
+        <v>0.06326507622984368</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,25 +4192,25 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0006099591325138091</v>
+        <v>-0.1312603674671504</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.04397496343654073</v>
+        <v>-0.004132498174468762</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.001236395193696958</v>
+        <v>0.0440883716314012</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -4225,46 +4225,46 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.02846288054200533</v>
+        <v>0.0800547321808092</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01920399686695174</v>
+        <v>-0.04550331880871085</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.004721508408080906</v>
+        <v>-0.0333533971815397</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02055128214727551</v>
+        <v>-0.09410108044756491</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0007410327843955027</v>
+        <v>-0.1280320338967604</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.009861698329155151</v>
+        <v>0.1353628973196861</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4273,67 +4273,67 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.01818973387333239</v>
+        <v>-0.1682916888408014</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.02205444862839919</v>
+        <v>-0.1246266609602856</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.02204418608864708</v>
+        <v>0.09355505120941257</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02227769508248134</v>
+        <v>-0.2982887152302066</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.001449126525695717</v>
+        <v>-0.03193496999840914</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02561994811334143</v>
+        <v>0.149520769465054</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.002601569919409065</v>
+        <v>-0.2211411433008695</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03062353771668422</v>
+        <v>0.1249458446716547</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02968635754804984</v>
+        <v>0.1495111937453435</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>0</v>
@@ -4357,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.01007154286165456</v>
+        <v>-0.1168168719961885</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,43 +4369,43 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.002462058157074802</v>
+        <v>0.08141258505106432</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0.001179123322380578</v>
+        <v>-0.005996610587777528</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01528909640594697</v>
+        <v>-0.1025958085097842</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.0263971870955855</v>
+        <v>0.009893154006465978</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4413,28 +4413,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2504683238931771</v>
+        <v>0.1903510124451937</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1229679854519454</v>
+        <v>-0.2036357200869431</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07727174759174683</v>
+        <v>0.004729804144386883</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>-0</v>
@@ -4443,16 +4443,16 @@
         <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2062692489771841</v>
+        <v>0.1785493643085841</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06984934494266222</v>
+        <v>-0.1619361573066751</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08192351563652073</v>
+        <v>-0.008327440126383511</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4464,55 +4464,55 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06963372516260316</v>
+        <v>0.07119976126213003</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01560873682807811</v>
+        <v>-0.03353056935918373</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09014134843964088</v>
+        <v>-0.1428715592301375</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1092194323978009</v>
+        <v>0.01973562412356951</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.01266305357097158</v>
+        <v>-0.1297354883870905</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.03028057610441907</v>
+        <v>-0.1007709535860942</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,25 +4521,25 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.002955563803124557</v>
+        <v>0.1507295662484825</v>
       </c>
       <c r="AM8" t="n">
         <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.06995287839372405</v>
+        <v>-0.08146559904231414</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.08587975649933814</v>
+        <v>0.05113814057318961</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4551,16 +4551,16 @@
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4206767743678621</v>
+        <v>0.3473685819424087</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.04603637712841038</v>
+        <v>-0.1294606524047251</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.07007249815580828</v>
+        <v>-0.246745321172158</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
@@ -4575,19 +4575,19 @@
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02905045295485938</v>
+        <v>-0.07439259855332568</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0630371490948476</v>
+        <v>-0.02593716592549065</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1006822678351326</v>
+        <v>-0.08501542209783874</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4605,16 +4605,16 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.08344912241635184</v>
+        <v>0.03144682178920514</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0645043622073876</v>
+        <v>0.05731716890525351</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1563259635390073</v>
+        <v>0.06854438489883316</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>-0</v>
@@ -4632,43 +4632,43 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2583528842366117</v>
+        <v>0.2230568993042917</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.02217235556269271</v>
+        <v>-0.1366439929808509</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.08962730308774886</v>
+        <v>-0.06827865460803142</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.07414573043889396</v>
+        <v>-0.1236512468997459</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.02434900244632972</v>
+        <v>0.1767483283218186</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0164800616265757</v>
+        <v>0.03377611644453602</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
@@ -4686,43 +4686,43 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.03141187896033966</v>
+        <v>-0.02313003503848896</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.03787394156398</v>
+        <v>0.2190120999123154</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.03467447111133664</v>
+        <v>0.04720335313893837</v>
       </c>
       <c r="CR8" t="n">
         <v>0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.06105940263808431</v>
+        <v>-0.1059656649475835</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.03571495239655658</v>
+        <v>0.1929811898490235</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01620419058732822</v>
+        <v>0.03655406680024974</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,43 +4740,43 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02037382976607875</v>
+        <v>-0.006430943994902342</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1213711220266858</v>
+        <v>0.07198281360432308</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001747868032107001</v>
+        <v>-0.01026862773099963</v>
       </c>
       <c r="DJ8" t="n">
         <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.06927651420046164</v>
+        <v>-0.08649182317867808</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.06751458271874709</v>
+        <v>0.1467169228900401</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.06745602009007357</v>
+        <v>-0.018372717942881</v>
       </c>
       <c r="DS8" t="n">
         <v>-0</v>
@@ -4791,19 +4791,19 @@
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.08869757910767896</v>
+        <v>-0.1296030902730533</v>
       </c>
       <c r="DY8" t="n">
         <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.02524469717876545</v>
+        <v>-0.07134260526336218</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.0245729687553588</v>
+        <v>-0.1625711160859899</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,34 +4812,34 @@
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08370801670032939</v>
+        <v>-0.04261711311773166</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.07401925681241145</v>
+        <v>0.1356718761244101</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.1209541604769908</v>
+        <v>0.04602359177497402</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
@@ -4848,43 +4848,43 @@
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.07443026861969591</v>
+        <v>-0.07585146379765528</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.03932295425795847</v>
+        <v>0.1205597648097567</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.06833677865078781</v>
+        <v>-0.004072544019573669</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
         <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.06254230091031318</v>
+        <v>-0.126019574717265</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.04777472603164204</v>
+        <v>0.1954303522508856</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.02048936259903957</v>
+        <v>0.01980327211398105</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
@@ -4893,34 +4893,34 @@
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.1082064883175548</v>
+        <v>-0.06077379552315471</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.04561281136842247</v>
+        <v>0.07739632459968551</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04489752985158375</v>
+        <v>-0.1426973238334933</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
@@ -4929,40 +4929,40 @@
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01442405086348018</v>
+        <v>-0.0135343948179393</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>-0.03279845004054632</v>
+        <v>-0.02098609799707796</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.0545482604261677</v>
+        <v>0.05754902115760417</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.05382552965482688</v>
+        <v>-0.09646617720044166</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.01669045410476921</v>
+        <v>0.166665328627763</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
@@ -4974,7 +4974,7 @@
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4982,7 +4982,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.09906733775562168</v>
+        <v>0.1082612958083329</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -4991,25 +4991,25 @@
         <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09022228299783001</v>
+        <v>-0.2079086325267085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0971762341509165</v>
+        <v>0.02918275486539133</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09590880212774408</v>
+        <v>0.06181713141233248</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -5018,25 +5018,25 @@
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03373609159318349</v>
+        <v>-0.2336936211677983</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04158153944377848</v>
+        <v>-0.01136047408136928</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02328456689148925</v>
+        <v>-0.02171307711836512</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -5045,40 +5045,40 @@
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06403932823605674</v>
+        <v>-0.05876543542923396</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0595990538854721</v>
+        <v>-0.04704304836992026</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.02434153909792487</v>
+        <v>0.01405663730034994</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01558899793351915</v>
+        <v>0.07677941923473028</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05864125455364617</v>
+        <v>0.1934972602238114</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5087,49 +5087,49 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.02008983386753889</v>
+        <v>0.02310636401289592</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03098385361694254</v>
+        <v>-0.1751247738810381</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.07442491210767864</v>
+        <v>0.070639941657691</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.08376138756308692</v>
+        <v>-0.05017770335772478</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.07287621340680769</v>
+        <v>-0.3687919678581894</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1810371455535923</v>
+        <v>-0.04364634563207771</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5144,7 +5144,7 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.111699901368557</v>
+        <v>0.1662825801778151</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -5153,37 +5153,37 @@
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01511656032618719</v>
+        <v>0.2495934882386688</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.067567298298853</v>
+        <v>0.1528886142606185</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0476686383706395</v>
+        <v>0.01978660823273725</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02547342294779504</v>
+        <v>0.01196571251010143</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1212335624494343</v>
+        <v>-0.1160309849972563</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
@@ -5192,25 +5192,25 @@
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.03873414398661346</v>
+        <v>-0.08028910920373446</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.004232478577554314</v>
+        <v>-0.3183181657248954</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.1012804429005192</v>
+        <v>-0.03486878669488625</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -5219,94 +5219,94 @@
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0.02563733346160264</v>
+        <v>-0.06033827668510361</v>
       </c>
       <c r="CE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.01030637227395413</v>
+        <v>0.1219380063411104</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02904510876494305</v>
+        <v>-0.01213980491692301</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0.01636844566050851</v>
+        <v>0.002044966299653163</v>
       </c>
       <c r="CN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.04157352580601639</v>
+        <v>0.07235119780947186</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.0303155777105983</v>
+        <v>-0.03423993959012413</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0.01394773344934914</v>
+        <v>-0.04592346671456254</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.003941567335601865</v>
+        <v>0.12074459605895</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.0194223594961514</v>
+        <v>0.007891751723051413</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0.01709633690700213</v>
+        <v>-0.01755700982653266</v>
       </c>
       <c r="DF9" t="n">
         <v>-0</v>
@@ -5315,13 +5315,13 @@
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.06780914475338308</v>
+        <v>0.1091513084259604</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.03899169031036098</v>
+        <v>-0.03037724547077557</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5330,106 +5330,106 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0.02850703970738228</v>
+        <v>-0.06520843056415769</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.03403828908737734</v>
+        <v>0.003032244032243534</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.06674248130066025</v>
+        <v>0.04729068298029045</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0.03692637061142695</v>
+        <v>0.02316395996368459</v>
       </c>
       <c r="DX9" t="n">
         <v>-0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02621426977659825</v>
+        <v>0.0594481875088207</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03137817327724351</v>
+        <v>0.0136085228935048</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0.01348424378580287</v>
+        <v>-0.08594166444119233</v>
       </c>
       <c r="EG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.02079933276091596</v>
+        <v>0.09312826691117368</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.007366372076027377</v>
+        <v>0.03901335489356527</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0.01137172688811216</v>
+        <v>0.02780115057349889</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02750010938246623</v>
+        <v>0.1187437178301348</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01969118648479748</v>
+        <v>0.01226857899510211</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5441,19 +5441,19 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0.01576984017966766</v>
+        <v>-0.05336740843160306</v>
       </c>
       <c r="EY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.002011874240542696</v>
+        <v>0.1600779960445394</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02354415360697751</v>
+        <v>-0.004706106443016408</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
@@ -5465,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0.02348578607141464</v>
+        <v>0.04070025471361075</v>
       </c>
       <c r="FH9" t="n">
         <v>0</v>
@@ -5477,52 +5477,52 @@
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.02648718043701603</v>
+        <v>0.09509100245193716</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.1017691954199991</v>
+        <v>0.1457356118731103</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
         <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.004097053682837848</v>
+        <v>0.007724576571590663</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.01201142186916436</v>
+        <v>0.2291545077514879</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.048375871175562</v>
+        <v>0.08106850380298727</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.01018473003137937</v>
+        <v>0.01724194585528445</v>
       </c>
       <c r="FZ9" t="n">
         <v>0</v>
@@ -5531,13 +5531,13 @@
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.01165913293691281</v>
+        <v>0.2388101357851574</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -6692,25 +6692,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3773513215241081</v>
+        <v>0.3600755275670357</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1306475099936757</v>
+        <v>-0.1736091754089946</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0327044899185948</v>
+        <v>-0.04563679617136352</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2253849729460149</v>
+        <v>0.3466479161148381</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1553142289898256</v>
+        <v>-0.2404137968560638</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.02473129864557112</v>
+        <v>-0.105250198392397</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,79 +6746,79 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.09865844191687652</v>
+        <v>0.06601136972906148</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0149369224900224</v>
+        <v>-0.08306860996203777</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1015625904133644</v>
+        <v>-0.1054975683963351</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05142274880668218</v>
+        <v>-0.04904996184278221</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.001760627985204008</v>
+        <v>-0.1616999992657494</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.008709615499033325</v>
+        <v>-0.06509619783736649</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.00245997350925448</v>
+        <v>0.1267331654058451</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0667619309626844</v>
+        <v>-0.1236227483044993</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04972722422092293</v>
+        <v>0.05725888655740769</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,25 +6827,25 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3666926778838401</v>
+        <v>0.3641768340661247</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02012187500149823</v>
+        <v>-0.08749546463842761</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1051793652543528</v>
+        <v>-0.2537253979828141</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.06028916155360685</v>
+        <v>-0.02405212380018257</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1645246218485479</v>
+        <v>-0.03412575320993668</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.105845917827912</v>
+        <v>-0.009306493320852677</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0923446893910989</v>
+        <v>0.0167599005847052</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05101021363331686</v>
+        <v>0.0397439377997031</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1698469295867305</v>
+        <v>0.05179015619758375</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,49 +6908,49 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1552743416057842</v>
+        <v>0.2297853022162297</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01598952878218591</v>
+        <v>-0.1565497204768699</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07218732133285256</v>
+        <v>-0.09090095458891796</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.09677195202292782</v>
+        <v>-0.1386971467853763</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.0006627063502073519</v>
+        <v>0.1208984373269038</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01248059041532537</v>
+        <v>0.01245224302648062</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.002185978100842842</v>
+        <v>-0.05188215433940337</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.06708330726583303</v>
+        <v>0.1588788301209448</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.03787532270281315</v>
+        <v>0.03803962821163685</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.07094041576446554</v>
+        <v>-0.1370978692119124</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03079832605330411</v>
+        <v>0.1335236146380131</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01642098806831442</v>
+        <v>0.02415318067240809</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7016,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.02960461102806624</v>
+        <v>-0.05904912595960561</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03775287231685556</v>
+        <v>0.04024271666985443</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07049600975642654</v>
+        <v>-0.1143622966017231</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
@@ -7040,28 +7040,28 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06833082658249658</v>
+        <v>-0.09308432279889399</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01757648486771068</v>
+        <v>-0.03110352811043342</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.04014728106032384</v>
+        <v>-0.0277094314783292</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,19 +7070,19 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.07767936048515726</v>
+        <v>-0.02616121984107535</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02027793337428219</v>
+        <v>0.07701011820036766</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.009321342680022753</v>
+        <v>-0.01707880587292466</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08780944296116698</v>
+        <v>-0.0885272207561706</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01179854880503621</v>
+        <v>0.08953887808544143</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05153321882795716</v>
+        <v>0.0491470175316461</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
@@ -7115,31 +7115,31 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.008847193745840091</v>
+        <v>-0.0482516639839193</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01102216536201043</v>
+        <v>0.08604572625446505</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0342327744572034</v>
+        <v>-0.001541019032264787</v>
       </c>
       <c r="ET12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,25 +7151,25 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06979266071579283</v>
+        <v>-0.1514552351513417</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.00701759763719823</v>
+        <v>0.1564919170006244</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01085909663677484</v>
+        <v>0.004890852898896263</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
@@ -7178,16 +7178,16 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.04123835391465855</v>
+        <v>0.1228333407283952</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0.006774435703172705</v>
+        <v>0.1035005756285889</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.02592363803474356</v>
+        <v>0.01018667610209771</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,58 +7196,58 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04534195593144383</v>
+        <v>0.05237918504056643</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.02196361231978971</v>
+        <v>0.1787543973419852</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.05564338897855672</v>
+        <v>-0.007862593457841835</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0545565672966507</v>
+        <v>-0.06241146878258833</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.1122349806478829</v>
+        <v>0.07379225205887437</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1127637924741442</v>
+        <v>0.2863493707931166</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,25 +7270,25 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03953674439613339</v>
+        <v>-0.01313722794131849</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06480811746664727</v>
+        <v>-0.1388375334155111</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08603638404856363</v>
+        <v>0.3254511395815915</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,133 +7297,133 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.02982915099548806</v>
+        <v>-0.08564679364180762</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.05116443516520322</v>
+        <v>-0.1485482061658589</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.005849286065448194</v>
+        <v>0.08219154258812326</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.005634113246032222</v>
+        <v>-0.1122341296533946</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0100924746629383</v>
+        <v>-0.01129577990747426</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.006215552674982092</v>
+        <v>-0.01854234492606003</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01469060631994691</v>
+        <v>-0.1956910107554663</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004472431678395505</v>
+        <v>0.03202528160614216</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.004236298297606433</v>
+        <v>0.03885901538959634</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01182729461532979</v>
+        <v>-0.02686294563612165</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01151536325996108</v>
+        <v>-0.005600717556363662</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0923431938052429</v>
+        <v>0.3258216241307262</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01438330059283411</v>
+        <v>-0.2242544077180345</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.01935799792801879</v>
+        <v>-0.09732354608834391</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03577736465431486</v>
+        <v>-0.01216465044548506</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,40 +7432,40 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.04910809156444342</v>
+        <v>0.0004435764811464228</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06103230788414317</v>
+        <v>-0.07665378314211575</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0353568565812406</v>
+        <v>0.04310932875108618</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02193927076676761</v>
+        <v>0.08235415619907052</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01627185112906335</v>
+        <v>0.003475372239181859</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04307207156668506</v>
+        <v>0.1900542672257735</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.008860810925025508</v>
+        <v>-0.06169355259193419</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.004342615524826775</v>
+        <v>-0.1142022439650167</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,31 +7498,31 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.02156639185035648</v>
+        <v>-0.09523327255527886</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.003208217616288648</v>
+        <v>0.01669570442201163</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02075551587325506</v>
+        <v>0.05849147259477324</v>
       </c>
       <c r="CJ13" t="n">
         <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.001209720048513479</v>
+        <v>-0.04637748634744659</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,64 +7540,64 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.00219777430508736</v>
+        <v>0.07320109974530845</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.009822296480234215</v>
+        <v>0.04424835101701568</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.0170992784940947</v>
+        <v>-0.09973580321812554</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005333275643870515</v>
+        <v>0.011961147657363</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02088857934932197</v>
+        <v>0.08003156392615968</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.01283942365986407</v>
+        <v>-0.02157691739446141</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01999902940594721</v>
+        <v>-0.1059135349554666</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0080516988697669</v>
+        <v>0.07327533904324736</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
@@ -7612,76 +7612,76 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.007553967552158528</v>
+        <v>-0.03842117501267878</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01911063798899288</v>
+        <v>-0.07576574409030633</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.005420578119751232</v>
+        <v>0.03232237818243903</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.0334237136770912</v>
+        <v>-0.0006517329032272564</v>
       </c>
       <c r="DY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01630791552697285</v>
+        <v>-0.02489121401307906</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01044091416600032</v>
+        <v>0.03374777905529543</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02347527255199616</v>
+        <v>-0.03427269480378123</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.00550750927340675</v>
+        <v>0.01079000043607709</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01773561582534959</v>
+        <v>0.01326234094138081</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7693,19 +7693,19 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01058870154768475</v>
+        <v>-0.02081597481986324</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.005649522765872213</v>
+        <v>0.001599864364988638</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.001732535512964909</v>
+        <v>0.08647778477482378</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.01706490085312081</v>
+        <v>-0.1108743519380647</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.009829800803523409</v>
+        <v>-0.00153262921448264</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02430079112690624</v>
+        <v>0.05302263890701542</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01994952707747709</v>
+        <v>0.1552355332784363</v>
       </c>
       <c r="FI13" t="n">
         <v>0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01200606653851579</v>
+        <v>-0.05873704376437226</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01766656222999259</v>
+        <v>0.1123734220129602</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.004670302416507168</v>
+        <v>0.04960198233120026</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,46 +7783,46 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0225092890044724</v>
+        <v>-0.08773658133370681</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.005668112125343812</v>
+        <v>-0.04198790786701405</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.002814198426432425</v>
+        <v>-0.03075853826680862</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.007740939661548513</v>
+        <v>0.08978448842994091</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,25 +7830,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4241515604193432</v>
+        <v>0.228223192556973</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1504116635598435</v>
+        <v>-0.1762933179782317</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04723471173479717</v>
+        <v>-0.04035115565709589</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7857,16 +7857,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2719783141465239</v>
+        <v>0.2317441561975882</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1504013729114322</v>
+        <v>-0.2175664229423637</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04440800195455714</v>
+        <v>-0.09785591972245564</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7878,112 +7878,112 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1030236830756604</v>
+        <v>0.05275498578536282</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0136043364136193</v>
+        <v>-0.05779678226468801</v>
       </c>
       <c r="W14" t="n">
-        <v>0.09650793445570266</v>
+        <v>-0.08800941485223797</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.03321356420043026</v>
+        <v>-0.03581117494521599</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.004594667477080567</v>
+        <v>-0.1283165657773133</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01046400583063729</v>
+        <v>-0.03762531715676642</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01066340935671226</v>
+        <v>0.0858992209942929</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06482190278292449</v>
+        <v>-0.1006692607598248</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.05092477411883083</v>
+        <v>0.02262110423278292</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4001604506282352</v>
+        <v>0.2218727994767666</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02373325819052171</v>
+        <v>-0.1018372996256354</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.09325506491508519</v>
+        <v>-0.2403798843876488</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,25 +7992,25 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.04934906222921837</v>
+        <v>-0.0123778292782962</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1671744366359123</v>
+        <v>-0.04734494890029767</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1023504487471429</v>
+        <v>-0.002861159175575367</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,19 +8019,19 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1150928017999751</v>
+        <v>0.0403026513310899</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04811163215843085</v>
+        <v>0.06054904820033095</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1665770273739919</v>
+        <v>0.04157784528600216</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8040,49 +8040,49 @@
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1786885514062124</v>
+        <v>0.1330067760387153</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01106349985835627</v>
+        <v>-0.1247930753479675</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.06933336526745899</v>
+        <v>-0.08840007316454331</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.09188166124434373</v>
+        <v>-0.06644095384737077</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.002578301462907715</v>
+        <v>0.1128749673306855</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01379174188985909</v>
+        <v>0.0185909074657036</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
@@ -8094,79 +8094,79 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.00571108001587647</v>
+        <v>-0.0200216176315489</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.06448028909585855</v>
+        <v>0.1402752202564683</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.06231872195920776</v>
+        <v>0.04806945036099308</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.064130065797926</v>
+        <v>-0.06460826109024502</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.03549940873661987</v>
+        <v>0.1232531072279359</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01933395068890391</v>
+        <v>0.02733470271853934</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.04688875280518688</v>
+        <v>-0.04547337510897874</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04409719713252983</v>
+        <v>0.02187210408791993</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.02882865800400706</v>
+        <v>-0.04586129270635336</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
@@ -8178,28 +8178,28 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.06869909093714839</v>
+        <v>-0.05162920168878236</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.007223996812084543</v>
+        <v>-0.03609343148343935</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.03779082070767744</v>
+        <v>-0.03276681571867181</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,19 +8208,19 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.09302157753411561</v>
+        <v>0.02008735431858054</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.01450286849839411</v>
+        <v>0.07486111010162813</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.03381551496233738</v>
+        <v>-0.05038702216332594</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
@@ -8229,85 +8229,85 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.08009332702994817</v>
+        <v>-0.04731064657858366</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.01476469466704782</v>
+        <v>0.09577211764367417</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.05807363449016865</v>
+        <v>0.05194478890842998</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.008468220951870125</v>
+        <v>0.02304123431211097</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.0008690332624334404</v>
+        <v>0.0631087662671026</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02817032339090816</v>
+        <v>-0.005243268595660707</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.06403188657200261</v>
+        <v>-0.07181051433948847</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.000973023053664577</v>
+        <v>0.1476381817804675</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.008652197095691948</v>
+        <v>0.003171440417384608</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>0</v>
@@ -8316,16 +8316,16 @@
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.06520562932374557</v>
+        <v>0.1293122257883401</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0005560582788154525</v>
+        <v>0.09479486226385633</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.04963748407682232</v>
+        <v>-0.02635360738512995</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8334,58 +8334,58 @@
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.04692321225048371</v>
+        <v>0.03866743258724739</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.01094442517642029</v>
+        <v>0.1356675864639633</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.06299873273382373</v>
+        <v>-0.06353417565867381</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.05971993709588939</v>
+        <v>0.001061451696646709</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.1128159022523102</v>
+        <v>0.03701531648255335</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3117274826242231</v>
+        <v>0.4995870357614384</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06541398118011278</v>
+        <v>0.01949625710353416</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2173948107544354</v>
+        <v>-0.3779138698751388</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8423,10 +8423,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2574758067136776</v>
+        <v>0.622796335067098</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.01325292359720689</v>
+        <v>-0.1274719771233237</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.174206528677299</v>
+        <v>-0.3880975965324727</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03439530343285629</v>
+        <v>0.1397789239353753</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,37 +8462,37 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.05628386869789571</v>
+        <v>-0.1317332555706931</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0006635982679708472</v>
+        <v>-0.1137116035209324</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.005222051315591821</v>
+        <v>-0.04822037469576693</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.006631047262658202</v>
+        <v>-0.2800212031603668</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.01798326692730248</v>
+        <v>0.1159558618345998</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05064797866701581</v>
+        <v>0.1260678392389503</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.006852967605895145</v>
+        <v>-0.08976623137489108</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.06416684042531878</v>
+        <v>-0.1194775786713884</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,37 +8531,37 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2221587967139153</v>
+        <v>0.7437601812730525</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.05209826450847264</v>
+        <v>-0.3816911806384023</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.1273795377957212</v>
+        <v>-0.302925403810792</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.07952585110330611</v>
+        <v>-0.1260241731356738</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.0522324698444698</v>
+        <v>0.05426712495396251</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.07986725155163034</v>
+        <v>-0.03973559209289819</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.07495080963346808</v>
+        <v>0.1617864475863007</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.02035253223999376</v>
+        <v>0.08564248802730039</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.02315236893792851</v>
+        <v>0.09009153636522302</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1255023545865961</v>
+        <v>0.3959614348810648</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,91 +8624,91 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04544087810277081</v>
+        <v>-0.06411540276476978</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.06151732152490759</v>
+        <v>-0.2678221264959463</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.0559358507041116</v>
+        <v>-0.1871646734928368</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.005941992411198973</v>
+        <v>0.05650494318659124</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.05947266247676423</v>
+        <v>0.1288448443616645</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.001839001150149725</v>
+        <v>-0.172989140974943</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.003116816143281438</v>
+        <v>0.1920543052013216</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.03245150094194756</v>
+        <v>0.02344351343654186</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.04857469724236153</v>
+        <v>-0.1733009738036952</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.003561357753942622</v>
+        <v>0.04328507317770893</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.06271563309659782</v>
+        <v>0.1620242923989608</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8717,25 +8717,25 @@
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.05754607395444504</v>
+        <v>-0.1569127654712215</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07065874991381733</v>
+        <v>-0.09853875437696302</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.001176884559068683</v>
+        <v>0.03747068062899955</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,13 +8744,13 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.01771405032067232</v>
+        <v>-0.1136587407110629</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
@@ -8759,16 +8759,16 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01943198286180844</v>
+        <v>-0.01897376954667964</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01275456027621039</v>
+        <v>0.1640488733400168</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
@@ -8777,46 +8777,46 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.04452521823957946</v>
+        <v>-0.07814230358244367</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02105387851167963</v>
+        <v>0.1072310304696311</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0332984859648091</v>
+        <v>0.0177105798525711</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.0521510009532336</v>
+        <v>-0.06773169847753842</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
         <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01149813948269677</v>
+        <v>-0.001455715572127775</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.06188708567019546</v>
+        <v>0.01667368019620645</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
@@ -8825,28 +8825,28 @@
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.03699780999366353</v>
+        <v>-0.06542294968353103</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.02230875092277708</v>
+        <v>-0.09222725403100759</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.01911890144061595</v>
+        <v>-0.04688187294752968</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,61 +8858,61 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.04860510551179947</v>
+        <v>-0.2102791904558943</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.003291147975511447</v>
+        <v>0.02075700793760852</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.06077510355799282</v>
+        <v>0.1381377837478286</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01608743564545934</v>
+        <v>0.1430305968939518</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.002221509993563922</v>
+        <v>-0.05315762379060271</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.03567462554738886</v>
+        <v>0.1752242563779777</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.001132522748251273</v>
+        <v>0.08467643584477738</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,37 +8921,37 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03934025259495959</v>
+        <v>-0.1217023483457736</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.03225537461166739</v>
+        <v>-0.08399091355010914</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.01514395254528187</v>
+        <v>-0.007460083710199255</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.02153796278632598</v>
+        <v>0.1967050114508536</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2380201270901641</v>
+        <v>0.3801088972054176</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,16 +8977,16 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04463890029866014</v>
+        <v>-0.04818642399111507</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2194939792317769</v>
+        <v>-0.1798506566783235</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2076452169507654</v>
+        <v>0.4610684728781204</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,25 +9004,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0184424089180516</v>
+        <v>-0.1696703044227142</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.161957683272358</v>
+        <v>-0.1829136314240734</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0186937918947255</v>
+        <v>0.1039148241784596</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,37 +9031,37 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02656040172501982</v>
+        <v>-0.1309589418394732</v>
       </c>
       <c r="X16" t="n">
-        <v>0.005362492853491348</v>
+        <v>-0.02107537039665941</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.009921474110385742</v>
+        <v>-0.04409458364326283</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01309602419043784</v>
+        <v>-0.2434886783125185</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.01162235363770577</v>
+        <v>0.05222276966429916</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.03679462231141199</v>
+        <v>0.02543793646756181</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.008088730569892375</v>
+        <v>-0.05898588718151545</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.035962508300517</v>
+        <v>0.01249612865721162</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1762614014956819</v>
+        <v>0.4523409942324362</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,16 +9112,16 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.03290147869936842</v>
+        <v>-0.2990900906957171</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.1119495226530865</v>
+        <v>-0.1575608202950972</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05856472748010225</v>
+        <v>-0.02753018179058724</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,52 +9139,52 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.05812239999551807</v>
+        <v>-0.0209940414613752</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.09045096029150596</v>
+        <v>-0.06415306399553877</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.06312113441400946</v>
+        <v>0.06909843563840605</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.01276243668563268</v>
+        <v>0.08994881124424943</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.02016396011919359</v>
+        <v>-0.0003881153621909424</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.09284848190433211</v>
+        <v>0.245090031865229</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.02608882900715333</v>
+        <v>-0.08552600451148583</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.03982267933287312</v>
+        <v>-0.09024615094745193</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9211,22 +9211,22 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03837024077422957</v>
+        <v>-0.1134838087901542</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.006492972690864979</v>
+        <v>0.03541674155894555</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.04922477626491382</v>
+        <v>0.06108018626721665</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,52 +9235,52 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.002677486905705086</v>
+        <v>-0.1222546075558408</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.009834891545317394</v>
+        <v>0.1461117943977293</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.02515789925992106</v>
+        <v>0.1008026497155244</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.02842660771748533</v>
+        <v>-0.1160957673814095</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.003517792715163522</v>
+        <v>0.02195847313047311</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.04951239309582588</v>
+        <v>0.08156258904384492</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
@@ -9292,46 +9292,46 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.02633849374784468</v>
+        <v>-0.04268285818389663</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02553102856872787</v>
+        <v>-0.1796604745616948</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.002619141428504842</v>
+        <v>0.02232689619676888</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.002190801974988592</v>
+        <v>-0.01220985861684473</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01881603078965897</v>
+        <v>-0.08645613389516908</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.01039866562648719</v>
+        <v>0.0677045797034778</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9340,13 +9340,13 @@
         <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.03271757175286671</v>
+        <v>-0.003148464091676574</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,10 +9355,10 @@
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.009313097509065131</v>
+        <v>-0.01828436807170635</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01892382336999404</v>
+        <v>0.02799535032659593</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
@@ -9370,25 +9370,25 @@
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.04169770661893946</v>
+        <v>-0.05237578834196016</v>
       </c>
       <c r="EH16" t="n">
         <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.006882683214358915</v>
+        <v>0.02090085115677771</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.05144468542508553</v>
+        <v>0.004164192437540469</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9400,61 +9400,61 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01261420815207577</v>
+        <v>-0.01808400212864439</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.01002289912075052</v>
+        <v>0.002191816098393776</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.03965724943197129</v>
+        <v>0.1193651947181323</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.02804218361638978</v>
+        <v>-0.129568384628751</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.0003695636334798011</v>
+        <v>0.008592599785250482</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.05011402843405117</v>
+        <v>0.0498054022852524</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.0100677912598894</v>
+        <v>0.2040567145334455</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.002015555413304542</v>
+        <v>-0.08188854312610831</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01720052571549123</v>
+        <v>0.1390628393984205</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,55 +9481,55 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.01197236998554341</v>
+        <v>0.07705834592034287</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.02289252224130313</v>
+        <v>-0.1284002253646416</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.02438496638260159</v>
+        <v>-0.06122044274965908</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.02000501425781653</v>
+        <v>-0.03382413365858077</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.02978472198713811</v>
+        <v>0.07891776144269004</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5309096024923872</v>
+        <v>0.3856514504487089</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1962484880942854</v>
+        <v>-0.4562662713261113</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1340642056922987</v>
+        <v>-0.1536898236134784</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3844722872760799</v>
+        <v>0.3383707284177859</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.159964625337749</v>
+        <v>-0.4729834782718894</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1406625725154408</v>
+        <v>-0.3250574976450354</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9588,28 +9588,28 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1501458252722636</v>
+        <v>0.08736234896041828</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.04093596805912528</v>
+        <v>-0.07595159366311915</v>
       </c>
       <c r="W17" t="n">
-        <v>0.06440335141943063</v>
+        <v>-0.1699733308242269</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -9618,43 +9618,43 @@
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1114725554232333</v>
+        <v>0.008397951867511541</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.005546328379867918</v>
+        <v>-0.1437963118652451</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.02532203021607482</v>
+        <v>-0.1448540280904759</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04388532984779332</v>
+        <v>0.2075816658284972</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.08565378234762283</v>
+        <v>-0.1776199529016932</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.08399113958654665</v>
+        <v>-0.03746936664940437</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
@@ -9663,31 +9663,31 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4121447525895183</v>
+        <v>0.3727787513087217</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.06177502376843284</v>
+        <v>-0.2875663487961226</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.06065845773157483</v>
+        <v>-0.5215505838595809</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
         <v>-0</v>
@@ -9699,16 +9699,16 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.06932521626255787</v>
+        <v>-0.03128794280887706</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.0665662384991489</v>
+        <v>-0.1128392372261139</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2091193864467583</v>
+        <v>0.1091727033925911</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,76 +9726,76 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1262753505558013</v>
+        <v>0.1320743490922999</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.08489069470847534</v>
+        <v>0.2167011719738545</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1560020245561011</v>
+        <v>0.06384011818871992</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1940853376799483</v>
+        <v>0.280955312057036</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.01584197342941715</v>
+        <v>-0.2503229699761909</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.02419974335018753</v>
+        <v>-0.1725820117129377</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.09914643906995099</v>
+        <v>-0.09689081973458977</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0288133911271204</v>
+        <v>0.2705347851895755</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.003567927733223258</v>
+        <v>0.05164336934342995</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,49 +9807,49 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.02849978148607945</v>
+        <v>-0.05879794412175526</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.09261074393985444</v>
+        <v>0.3099403819247418</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.04747568170700708</v>
+        <v>0.1024029483312167</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.08853435424610547</v>
+        <v>-0.08190559392306022</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.05837928596695884</v>
+        <v>0.2867844537770141</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.003536867158084418</v>
+        <v>0.08797001751065442</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,25 +9861,25 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.02928110322185808</v>
+        <v>-0.1147762496721865</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0.0007032556030786964</v>
+        <v>-0.02838579905533811</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04943834968269278</v>
+        <v>-0.1137091986571816</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
         <v>0</v>
@@ -9888,16 +9888,16 @@
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.001979239003762691</v>
+        <v>-0.1340595864249777</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.111548498016489</v>
+        <v>0.03455776017000221</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.04550780977538416</v>
+        <v>0.05481794687705103</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
@@ -9906,7 +9906,7 @@
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,16 +9915,16 @@
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.08629231891454786</v>
+        <v>0.06089973287973872</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.01212962360431274</v>
+        <v>0.1591713784207479</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.04706209755794252</v>
+        <v>-0.06844226057019974</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
@@ -9933,58 +9933,58 @@
         <v>0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.1072850495954981</v>
+        <v>-0.0260024241681069</v>
       </c>
       <c r="EH17" t="n">
         <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.06533647457588114</v>
+        <v>0.2258192898622783</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.08707759905442007</v>
+        <v>0.05633080143614799</v>
       </c>
       <c r="EK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.08636342071958547</v>
+        <v>-0.0547485832847505</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>-0.06646485587868371</v>
+        <v>-0.2157092825584848</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0004379765614310488</v>
+        <v>-0.01664871347770657</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,25 +9993,25 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.08592330151910577</v>
+        <v>-0.1160327003954715</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0359775028467232</v>
+        <v>0.3137748331831855</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.01595208798865327</v>
+        <v>0.0403671353551274</v>
       </c>
       <c r="FC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10020,19 +10020,19 @@
         <v>0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.05320476298267475</v>
+        <v>0.1111189800532998</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.08365635486164734</v>
+        <v>0.1953455800613784</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.02228890847955877</v>
+        <v>-0.03938578411769555</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10041,61 +10041,61 @@
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.01276156388595307</v>
+        <v>0.02710895688739692</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.06340753285871699</v>
+        <v>0.2684925370818458</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.009354924269047082</v>
+        <v>-0.1103626442292858</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.04704806096122351</v>
+        <v>0.04876948506823624</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.07698524732496445</v>
+        <v>0.1767882816069995</v>
       </c>
       <c r="GC17" t="n">
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
@@ -10103,10 +10103,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2521237159803796</v>
+        <v>0.519022922561875</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05873992132634599</v>
+        <v>-0.04488917344854914</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1985546671881663</v>
+        <v>-0.4105766495212397</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
@@ -10127,13 +10127,13 @@
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2283186213487451</v>
+        <v>0.6654138328127865</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,64 +10142,64 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.01953984397971768</v>
+        <v>-0.1939852693957323</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1417335966290286</v>
+        <v>-0.4075856123662687</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0187885506987371</v>
+        <v>0.1372558331358201</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.02728168840191828</v>
+        <v>-0.1089876666283394</v>
       </c>
       <c r="X18" t="n">
-        <v>-8.50714946099999e-05</v>
+        <v>-0.07526516950782365</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.002094745352202456</v>
+        <v>-0.06072661086096562</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.005081063033894218</v>
+        <v>-0.2872931023524127</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.007190611648787907</v>
+        <v>0.1092863644479519</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.02806022301412315</v>
+        <v>0.1226161936504729</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.00453065294198328</v>
+        <v>-0.04169800516754105</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.04651428234015046</v>
+        <v>-0.08293182041590805</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1446981680977391</v>
+        <v>0.6613005964513121</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,25 +10250,25 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.03173027571954828</v>
+        <v>-0.3098130189458019</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.113084074265578</v>
+        <v>-0.3231699491754152</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.05976819074514804</v>
+        <v>-0.08987412160099394</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,25 +10277,25 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.03848556786442719</v>
+        <v>-0.03600861380320628</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.06034275405558981</v>
+        <v>-0.03951130407414213</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
         <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05845548989265143</v>
+        <v>0.1353120086430671</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
@@ -10304,118 +10304,118 @@
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.01860566287628147</v>
+        <v>0.06682611310305893</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01770213586161997</v>
+        <v>0.07097490846572901</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.08247394128077959</v>
+        <v>0.3680927948356272</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.03123895837801272</v>
+        <v>-0.08497610960758817</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.03568310111031084</v>
+        <v>-0.1739796582338521</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD18" t="n">
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.0355395573307886</v>
+        <v>-0.1507293068311164</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.004655315809082722</v>
+        <v>0.06528069184648301</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.04214337563515731</v>
+        <v>0.10255606487947</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.003573917384674308</v>
+        <v>-0.2410148877635986</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.004880220143428125</v>
+        <v>0.2038675699011357</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.04371748955348605</v>
+        <v>0.01835065156460425</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.03176183142828301</v>
+        <v>-0.1461425269646365</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.0005292818709657615</v>
+        <v>0.04218041845793669</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.04389339166064123</v>
+        <v>0.14300995251582</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10424,58 +10424,58 @@
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.005845931542545459</v>
+        <v>0.0141541018239467</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.04809865940544408</v>
+        <v>-0.1313584930767523</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.003355454173233257</v>
+        <v>0.03412429633329329</v>
       </c>
       <c r="DK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.002642454717211384</v>
+        <v>-0.08621199339201918</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01383722999029774</v>
+        <v>0.02270572054919769</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.01191212738900006</v>
+        <v>0.126388790600333</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>0</v>
@@ -10484,79 +10484,79 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.0492970157786657</v>
+        <v>-0.06365576649596101</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01952917165009367</v>
+        <v>0.01376483542926447</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.01899846210111055</v>
+        <v>0.03950653164157924</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.03819692529492387</v>
+        <v>-0.03616040904807231</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.01247185356623008</v>
+        <v>-0.01448161302290622</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.04417047586334866</v>
+        <v>0.0232300577009319</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.02331009601736762</v>
+        <v>-0.03271359594397874</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.0165743333582769</v>
+        <v>-0.09104750924947981</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.002611146687283755</v>
+        <v>0.008363811133862078</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW18" t="n">
         <v>-0</v>
@@ -10565,61 +10565,61 @@
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.03353310534360893</v>
+        <v>-0.1730037905874527</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.001650397340909426</v>
+        <v>0.01479052126298267</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.04475019825473207</v>
+        <v>0.1200034910501969</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01953182928868775</v>
+        <v>0.1463316581504215</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.004596627691451316</v>
+        <v>-0.07562989318443324</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.03998218802692283</v>
+        <v>0.1833463528764804</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.002401812314856169</v>
+        <v>0.05274860118369525</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,37 +10628,37 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.03186237441927866</v>
+        <v>-0.1268261806644628</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.02321460701693641</v>
+        <v>-0.1454615709017769</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.02565781321593598</v>
+        <v>-0.01899540438444769</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.02515973758183819</v>
+        <v>0.1925126419714358</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
